--- a/template/pricing_tool_template.xlsx
+++ b/template/pricing_tool_template.xlsx
@@ -13,8 +13,7 @@
     <sheet name="O (UE3)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="O (UE4)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sheet9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Catalogue" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'O (UE)'!$2:$2</definedName>
@@ -541,23 +540,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H2" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:H73"/>
-  <tableColumns count="8">
-    <tableColumn id="18" name="Item No.1"/>
-    <tableColumn id="19" name="Description"/>
-    <tableColumn id="21" name="Unit Price"/>
-    <tableColumn id="24" name="Advanced Reserved"/>
-    <tableColumn id="26" name="Stock Available Quantity"/>
-    <tableColumn id="32" name="PO Qty"/>
-    <tableColumn id="33" name="PO not Shipped"/>
-    <tableColumn id="38" name="Landed USD"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A1:H2" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:H18"/>
   <tableColumns count="8">
     <tableColumn id="18" name="Item No.1"/>
     <tableColumn id="19" name="Description"/>
@@ -3056,83 +3038,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="36.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="20" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="24.140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="9" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="64" t="inlineStr">
-        <is>
-          <t>Item No.1</t>
-        </is>
-      </c>
-      <c r="B1" s="64" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" s="64" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="D1" s="64" t="inlineStr">
-        <is>
-          <t>Advanced Reserved</t>
-        </is>
-      </c>
-      <c r="E1" s="64" t="inlineStr">
-        <is>
-          <t>Stock Available Quantity</t>
-        </is>
-      </c>
-      <c r="F1" s="64" t="inlineStr">
-        <is>
-          <t>PO Qty</t>
-        </is>
-      </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t>PO not Shipped</t>
-        </is>
-      </c>
-      <c r="H1" s="64" t="inlineStr">
-        <is>
-          <t>Landed USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="65" t="n"/>
-      <c r="B2" s="65" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>